--- a/downloads/Ratio_pre_post_results.xlsx
+++ b/downloads/Ratio_pre_post_results.xlsx
@@ -964,7 +964,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pre/post designs only</t>
+          <t>Excluding crossover design - Lancaster et al. (2005)</t>
         </is>
       </c>
       <c r="C4">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Pre/post designs only</t>
+          <t>Excluding crossover design - Lancaster et al. (2005)</t>
         </is>
       </c>
       <c r="C7">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Pre/post designs only</t>
+          <t>Excluding crossover design - Lancaster et al. (2005)</t>
         </is>
       </c>
       <c r="C10">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Pre/post designs only</t>
+          <t>Excluding crossover design - Lancaster et al. (2005)</t>
         </is>
       </c>
       <c r="C13">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Pre/post designs only</t>
+          <t>Excluding crossover design - Lancaster et al. (2005)</t>
         </is>
       </c>
       <c r="C16">

--- a/downloads/Ratio_pre_post_results.xlsx
+++ b/downloads/Ratio_pre_post_results.xlsx
@@ -824,7 +824,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -997,39 +997,39 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Main analysis</t>
+          <t>Excluding absolute cell counts - Tsubakihara et al. (2012)</t>
         </is>
       </c>
       <c r="C5">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D5">
-        <v>0.306040363515574</v>
+        <v>0.3961884450611168</v>
       </c>
       <c r="E5">
-        <v>-0.05435228167602668</v>
+        <v>0.05681838534042266</v>
       </c>
       <c r="F5">
-        <v>0.6664330087071747</v>
+        <v>0.735558504781811</v>
       </c>
       <c r="G5">
-        <v>0.09071149404070347</v>
+        <v>0.02507782318820613</v>
       </c>
       <c r="H5">
-        <v>0.4147715730007523</v>
+        <v>0.3313744276959962</v>
       </c>
       <c r="I5">
-        <v>0.7707585571368664</v>
+        <v>0.6564598016922801</v>
       </c>
       <c r="J5">
-        <v>-1.108682648549973</v>
+        <v>-0.8822795779370449</v>
       </c>
       <c r="K5">
-        <v>1.720763375581121</v>
+        <v>1.674656468059279</v>
       </c>
     </row>
     <row r="6">
@@ -1038,35 +1038,35 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Lancaster et al. (2005) - n / 3</t>
+          <t>Main analysis</t>
         </is>
       </c>
       <c r="C6">
         <v>17</v>
       </c>
       <c r="D6">
-        <v>0.3284728587882637</v>
+        <v>0.306040363515574</v>
       </c>
       <c r="E6">
-        <v>-0.03832574513681486</v>
+        <v>-0.05435228167602668</v>
       </c>
       <c r="F6">
-        <v>0.6952714627133422</v>
+        <v>0.6664330087071747</v>
       </c>
       <c r="G6">
-        <v>0.07583206105313851</v>
+        <v>0.09071149404070347</v>
       </c>
       <c r="H6">
-        <v>0.3684295238682482</v>
+        <v>0.4147715730007523</v>
       </c>
       <c r="I6">
-        <v>0.7619550542717481</v>
+        <v>0.7707585571368664</v>
       </c>
       <c r="J6">
-        <v>-1.008869315434121</v>
+        <v>-1.108682648549973</v>
       </c>
       <c r="K6">
-        <v>1.665815033010648</v>
+        <v>1.720763375581121</v>
       </c>
     </row>
     <row r="7">
@@ -1075,109 +1075,109 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Excluding crossover design - Lancaster et al. (2005)</t>
+          <t>Lancaster et al. (2005) - n / 3</t>
         </is>
       </c>
       <c r="C7">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D7">
-        <v>0.374394738238146</v>
+        <v>0.3284728587882637</v>
       </c>
       <c r="E7">
-        <v>-0.06130985979518833</v>
+        <v>-0.03832574513681486</v>
       </c>
       <c r="F7">
-        <v>0.8100993362714802</v>
+        <v>0.6952714627133422</v>
       </c>
       <c r="G7">
-        <v>0.08620274551577925</v>
+        <v>0.07583206105313851</v>
       </c>
       <c r="H7">
-        <v>0.5055082364419538</v>
+        <v>0.3684295238682482</v>
       </c>
       <c r="I7">
-        <v>0.8023152197094948</v>
+        <v>0.7619550542717481</v>
       </c>
       <c r="J7">
-        <v>-1.226021715464505</v>
+        <v>-1.008869315434121</v>
       </c>
       <c r="K7">
-        <v>1.974811191940797</v>
+        <v>1.665815033010648</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Main analysis</t>
+          <t>Excluding crossover design - Lancaster et al. (2005)</t>
         </is>
       </c>
       <c r="C8">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D8">
-        <v>0.3004823493441052</v>
+        <v>0.374394738238146</v>
       </c>
       <c r="E8">
-        <v>-0.05583405126769231</v>
+        <v>-0.06130985979518833</v>
       </c>
       <c r="F8">
-        <v>0.6567987499559027</v>
+        <v>0.8100993362714802</v>
       </c>
       <c r="G8">
-        <v>0.09277492865247931</v>
+        <v>0.08620274551577925</v>
       </c>
       <c r="H8">
-        <v>0.4155819918163415</v>
+        <v>0.5055082364419538</v>
       </c>
       <c r="I8">
-        <v>0.8057492307088889</v>
+        <v>0.8023152197094948</v>
       </c>
       <c r="J8">
-        <v>-1.113940113225449</v>
+        <v>-1.226021715464505</v>
       </c>
       <c r="K8">
-        <v>1.714904811913659</v>
+        <v>1.974811191940797</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Lancaster et al. (2005) - n / 3</t>
+          <t>Excluding absolute cell counts - Tsubakihara et al. (2012)</t>
         </is>
       </c>
       <c r="C9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D9">
-        <v>0.3201722041285595</v>
+        <v>0.3902999197456626</v>
       </c>
       <c r="E9">
-        <v>-0.04212911894134252</v>
+        <v>0.05292237616169337</v>
       </c>
       <c r="F9">
-        <v>0.6824735271984615</v>
+        <v>0.7276774633296318</v>
       </c>
       <c r="G9">
-        <v>0.07939832365473491</v>
+        <v>0.02621446630668261</v>
       </c>
       <c r="H9">
-        <v>0.3769730503401492</v>
+        <v>0.3365677170755043</v>
       </c>
       <c r="I9">
-        <v>0.7983457251237102</v>
+        <v>0.7014144611327183</v>
       </c>
       <c r="J9">
-        <v>-1.030231019186677</v>
+        <v>-0.8959937912179324</v>
       </c>
       <c r="K9">
-        <v>1.670575427443796</v>
+        <v>1.676593630709258</v>
       </c>
     </row>
     <row r="10">
@@ -1186,151 +1186,151 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Excluding crossover design - Lancaster et al. (2005)</t>
+          <t>Main analysis</t>
         </is>
       </c>
       <c r="C10">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D10">
-        <v>0.368346327627224</v>
+        <v>0.3004823493441052</v>
       </c>
       <c r="E10">
-        <v>-0.06232875149599337</v>
+        <v>-0.05583405126769231</v>
       </c>
       <c r="F10">
-        <v>0.7990214067504414</v>
+        <v>0.6567987499559027</v>
       </c>
       <c r="G10">
-        <v>0.08751888461054262</v>
+        <v>0.09277492865247931</v>
       </c>
       <c r="H10">
-        <v>0.5022112980252346</v>
+        <v>0.4155819918163415</v>
       </c>
       <c r="I10">
-        <v>0.8325662205474649</v>
+        <v>0.8057492307088889</v>
       </c>
       <c r="J10">
-        <v>-1.225114098653088</v>
+        <v>-1.113940113225449</v>
       </c>
       <c r="K10">
-        <v>1.961806753907536</v>
+        <v>1.714904811913659</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Main analysis</t>
+          <t>Lancaster et al. (2005) - n / 3</t>
         </is>
       </c>
       <c r="C11">
         <v>17</v>
       </c>
       <c r="D11">
-        <v>0.2937355808048764</v>
+        <v>0.3201722041285595</v>
       </c>
       <c r="E11">
-        <v>-0.05634635991018538</v>
+        <v>-0.04212911894134252</v>
       </c>
       <c r="F11">
-        <v>0.6438175215199382</v>
+        <v>0.6824735271984615</v>
       </c>
       <c r="G11">
-        <v>0.0942923581936335</v>
+        <v>0.07939832365473491</v>
       </c>
       <c r="H11">
-        <v>0.4107910506025729</v>
+        <v>0.3769730503401492</v>
       </c>
       <c r="I11">
-        <v>0.8409100241886502</v>
+        <v>0.7983457251237102</v>
       </c>
       <c r="J11">
-        <v>-1.110922307641152</v>
+        <v>-1.030231019186677</v>
       </c>
       <c r="K11">
-        <v>1.698393469250904</v>
+        <v>1.670575427443796</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lancaster et al. (2005) - n / 3</t>
+          <t>Excluding crossover design - Lancaster et al. (2005)</t>
         </is>
       </c>
       <c r="C12">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D12">
-        <v>0.3104715585290475</v>
+        <v>0.368346327627224</v>
       </c>
       <c r="E12">
-        <v>-0.04499034515911537</v>
+        <v>-0.06232875149599337</v>
       </c>
       <c r="F12">
-        <v>0.6659334622172104</v>
+        <v>0.7990214067504414</v>
       </c>
       <c r="G12">
-        <v>0.08262971004348391</v>
+        <v>0.08751888461054262</v>
       </c>
       <c r="H12">
-        <v>0.3799146472988599</v>
+        <v>0.5022112980252346</v>
       </c>
       <c r="I12">
-        <v>0.8349124237672773</v>
+        <v>0.8325662205474649</v>
       </c>
       <c r="J12">
-        <v>-1.042994191710672</v>
+        <v>-1.225114098653088</v>
       </c>
       <c r="K12">
-        <v>1.663937308768766</v>
+        <v>1.961806753907536</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Excluding crossover design - Lancaster et al. (2005)</t>
+          <t>Excluding absolute cell counts - Tsubakihara et al. (2012)</t>
         </is>
       </c>
       <c r="C13">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D13">
-        <v>0.360823894405671</v>
+        <v>0.3833427672804874</v>
       </c>
       <c r="E13">
-        <v>-0.06216566831676518</v>
+        <v>0.04939425557646177</v>
       </c>
       <c r="F13">
-        <v>0.7838134571281071</v>
+        <v>0.7172912789845129</v>
       </c>
       <c r="G13">
-        <v>0.08826344840434226</v>
+        <v>0.02721658137663521</v>
       </c>
       <c r="H13">
-        <v>0.4923021010704767</v>
+        <v>0.338176473602035</v>
       </c>
       <c r="I13">
-        <v>0.8629628228266585</v>
+        <v>0.7465516850950908</v>
       </c>
       <c r="J13">
-        <v>-1.215188166548666</v>
+        <v>-0.9040092530180264</v>
       </c>
       <c r="K13">
-        <v>1.936835955360008</v>
+        <v>1.670694787579001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1341,33 +1341,33 @@
         <v>17</v>
       </c>
       <c r="D14">
-        <v>0.2850013866077368</v>
+        <v>0.2937355808048764</v>
       </c>
       <c r="E14">
-        <v>-0.05521587406379447</v>
+        <v>-0.05634635991018538</v>
       </c>
       <c r="F14">
-        <v>0.625218647279268</v>
+        <v>0.6438175215199382</v>
       </c>
       <c r="G14">
-        <v>0.0947762866906427</v>
+        <v>0.0942923581936335</v>
       </c>
       <c r="H14">
-        <v>0.3970838117590871</v>
+        <v>0.4107910506025729</v>
       </c>
       <c r="I14">
-        <v>0.8763402941060433</v>
+        <v>0.8409100241886502</v>
       </c>
       <c r="J14">
-        <v>-1.094528125977748</v>
+        <v>-1.110922307641152</v>
       </c>
       <c r="K14">
-        <v>1.664530899193221</v>
+        <v>1.698393469250904</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1378,33 +1378,33 @@
         <v>17</v>
       </c>
       <c r="D15">
-        <v>0.2985397782505866</v>
+        <v>0.3104715585290475</v>
       </c>
       <c r="E15">
-        <v>-0.04624171359617874</v>
+        <v>-0.04499034515911537</v>
       </c>
       <c r="F15">
-        <v>0.6433212700973521</v>
+        <v>0.6659334622172104</v>
       </c>
       <c r="G15">
-        <v>0.08507524316284511</v>
+        <v>0.08262971004348391</v>
       </c>
       <c r="H15">
-        <v>0.3739389274813147</v>
+        <v>0.3799146472988599</v>
       </c>
       <c r="I15">
-        <v>0.8717565638805077</v>
+        <v>0.8349124237672773</v>
       </c>
       <c r="J15">
-        <v>-1.042189253458045</v>
+        <v>-1.042994191710672</v>
       </c>
       <c r="K15">
-        <v>1.639268809959219</v>
+        <v>1.663937308768766</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1415,28 +1415,213 @@
         <v>14</v>
       </c>
       <c r="D16">
+        <v>0.360823894405671</v>
+      </c>
+      <c r="E16">
+        <v>-0.06216566831676518</v>
+      </c>
+      <c r="F16">
+        <v>0.7838134571281071</v>
+      </c>
+      <c r="G16">
+        <v>0.08826344840434226</v>
+      </c>
+      <c r="H16">
+        <v>0.4923021010704767</v>
+      </c>
+      <c r="I16">
+        <v>0.8629628228266585</v>
+      </c>
+      <c r="J16">
+        <v>-1.215188166548666</v>
+      </c>
+      <c r="K16">
+        <v>1.936835955360008</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.6</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Excluding absolute cell counts - Tsubakihara et al. (2012)</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>16</v>
+      </c>
+      <c r="D17">
+        <v>0.374824680046364</v>
+      </c>
+      <c r="E17">
+        <v>0.04653766269578963</v>
+      </c>
+      <c r="F17">
+        <v>0.7031116973969384</v>
+      </c>
+      <c r="G17">
+        <v>0.02792591754984281</v>
+      </c>
+      <c r="H17">
+        <v>0.3345832675347429</v>
+      </c>
+      <c r="I17">
+        <v>0.7919579551899034</v>
+      </c>
+      <c r="J17">
+        <v>-0.9037893581960974</v>
+      </c>
+      <c r="K17">
+        <v>1.653438718288825</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.7</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Main analysis</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>17</v>
+      </c>
+      <c r="D18">
+        <v>0.2850013866077368</v>
+      </c>
+      <c r="E18">
+        <v>-0.05521587406379447</v>
+      </c>
+      <c r="F18">
+        <v>0.625218647279268</v>
+      </c>
+      <c r="G18">
+        <v>0.0947762866906427</v>
+      </c>
+      <c r="H18">
+        <v>0.3970838117590871</v>
+      </c>
+      <c r="I18">
+        <v>0.8763402941060433</v>
+      </c>
+      <c r="J18">
+        <v>-1.094528125977748</v>
+      </c>
+      <c r="K18">
+        <v>1.664530899193221</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.7</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Lancaster et al. (2005) - n / 3</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>17</v>
+      </c>
+      <c r="D19">
+        <v>0.2985397782505866</v>
+      </c>
+      <c r="E19">
+        <v>-0.04624171359617874</v>
+      </c>
+      <c r="F19">
+        <v>0.6433212700973521</v>
+      </c>
+      <c r="G19">
+        <v>0.08507524316284511</v>
+      </c>
+      <c r="H19">
+        <v>0.3739389274813147</v>
+      </c>
+      <c r="I19">
+        <v>0.8717565638805077</v>
+      </c>
+      <c r="J19">
+        <v>-1.042189253458045</v>
+      </c>
+      <c r="K19">
+        <v>1.639268809959219</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.7</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Excluding crossover design - Lancaster et al. (2005)</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>14</v>
+      </c>
+      <c r="D20">
         <v>0.3507976607974506</v>
       </c>
-      <c r="E16">
+      <c r="E20">
         <v>-0.06006270150889509</v>
       </c>
-      <c r="F16">
+      <c r="F20">
         <v>0.7616580231037962</v>
       </c>
-      <c r="G16">
+      <c r="G20">
         <v>0.0880040804198378</v>
       </c>
-      <c r="H16">
+      <c r="H20">
         <v>0.4719199457597339</v>
       </c>
-      <c r="I16">
+      <c r="I20">
         <v>0.893588197363458</v>
       </c>
-      <c r="J16">
+      <c r="J20">
         <v>-1.190677058019738</v>
       </c>
-      <c r="K16">
+      <c r="K20">
         <v>1.892272379614639</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.7</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Excluding absolute cell counts - Tsubakihara et al. (2012)</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>16</v>
+      </c>
+      <c r="D21">
+        <v>0.3637087559891201</v>
+      </c>
+      <c r="E21">
+        <v>0.04481770085063186</v>
+      </c>
+      <c r="F21">
+        <v>0.6825998111276083</v>
+      </c>
+      <c r="G21">
+        <v>0.02806829913272466</v>
+      </c>
+      <c r="H21">
+        <v>0.3228980837148246</v>
+      </c>
+      <c r="I21">
+        <v>0.8377893537490601</v>
+      </c>
+      <c r="J21">
+        <v>-0.8906254402384832</v>
+      </c>
+      <c r="K21">
+        <v>1.618042952216723</v>
       </c>
     </row>
   </sheetData>

--- a/downloads/Ratio_pre_post_results.xlsx
+++ b/downloads/Ratio_pre_post_results.xlsx
@@ -824,7 +824,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -883,6 +883,46 @@
           <t>pi_upper</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>eg_t</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>eg_df</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>eg_p</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>tf_k0</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>tf_side</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>tf_g</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>tf_lo</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>tf_up</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -920,6 +960,32 @@
       <c r="K2">
         <v>1.719396034290935</v>
       </c>
+      <c r="L2">
+        <v>-0.5130353339114841</v>
+      </c>
+      <c r="M2">
+        <v>15</v>
+      </c>
+      <c r="N2">
+        <v>0.6153990303487498</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="Q2">
+        <v>0.3107873791843226</v>
+      </c>
+      <c r="R2">
+        <v>-0.03627582685668668</v>
+      </c>
+      <c r="S2">
+        <v>0.657850585225332</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3">
@@ -957,6 +1023,32 @@
       <c r="K3">
         <v>1.653009719790848</v>
       </c>
+      <c r="L3">
+        <v>-0.5337662673897293</v>
+      </c>
+      <c r="M3">
+        <v>15</v>
+      </c>
+      <c r="N3">
+        <v>0.6013243022019897</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="Q3">
+        <v>0.3357668279000747</v>
+      </c>
+      <c r="R3">
+        <v>-0.003783992360614719</v>
+      </c>
+      <c r="S3">
+        <v>0.6753176481607641</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4">
@@ -994,6 +1086,32 @@
       <c r="K4">
         <v>1.979768191474077</v>
       </c>
+      <c r="L4">
+        <v>-0.1604519879446908</v>
+      </c>
+      <c r="M4">
+        <v>12</v>
+      </c>
+      <c r="N4">
+        <v>0.8751944131541738</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="Q4">
+        <v>0.3794536193972495</v>
+      </c>
+      <c r="R4">
+        <v>-0.03363616936194064</v>
+      </c>
+      <c r="S4">
+        <v>0.7925434081564398</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5">
@@ -1031,6 +1149,32 @@
       <c r="K5">
         <v>1.674656468059279</v>
       </c>
+      <c r="L5">
+        <v>-0.5164641607313388</v>
+      </c>
+      <c r="M5">
+        <v>14</v>
+      </c>
+      <c r="N5">
+        <v>0.6135912154503909</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="Q5">
+        <v>0.3961884450611171</v>
+      </c>
+      <c r="R5">
+        <v>0.06589264503610098</v>
+      </c>
+      <c r="S5">
+        <v>0.7264842450861331</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6">
@@ -1068,6 +1212,32 @@
       <c r="K6">
         <v>1.720763375581121</v>
       </c>
+      <c r="L6">
+        <v>-0.5217549187114592</v>
+      </c>
+      <c r="M6">
+        <v>15</v>
+      </c>
+      <c r="N6">
+        <v>0.609459616020555</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="Q6">
+        <v>0.3060403635155741</v>
+      </c>
+      <c r="R6">
+        <v>-0.03674103495113196</v>
+      </c>
+      <c r="S6">
+        <v>0.64882176198228</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7">
@@ -1105,6 +1275,32 @@
       <c r="K7">
         <v>1.665815033010648</v>
       </c>
+      <c r="L7">
+        <v>-0.5375740566199481</v>
+      </c>
+      <c r="M7">
+        <v>15</v>
+      </c>
+      <c r="N7">
+        <v>0.5987565986374399</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="Q7">
+        <v>0.3284728587882636</v>
+      </c>
+      <c r="R7">
+        <v>-0.008402411813998367</v>
+      </c>
+      <c r="S7">
+        <v>0.6653481293905256</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8">
@@ -1142,6 +1338,32 @@
       <c r="K8">
         <v>1.974811191940797</v>
       </c>
+      <c r="L8">
+        <v>-0.1658419232139831</v>
+      </c>
+      <c r="M8">
+        <v>12</v>
+      </c>
+      <c r="N8">
+        <v>0.8710426636904186</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="Q8">
+        <v>0.3743947382381459</v>
+      </c>
+      <c r="R8">
+        <v>-0.03338580315146905</v>
+      </c>
+      <c r="S8">
+        <v>0.7821752796277608</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9">
@@ -1179,6 +1401,32 @@
       <c r="K9">
         <v>1.676593630709258</v>
       </c>
+      <c r="L9">
+        <v>-0.527341610025517</v>
+      </c>
+      <c r="M9">
+        <v>14</v>
+      </c>
+      <c r="N9">
+        <v>0.6062129619470562</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="Q9">
+        <v>0.3902999197456627</v>
+      </c>
+      <c r="R9">
+        <v>0.06454413978711887</v>
+      </c>
+      <c r="S9">
+        <v>0.7160556997042065</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10">
@@ -1216,6 +1464,32 @@
       <c r="K10">
         <v>1.714904811913659</v>
       </c>
+      <c r="L10">
+        <v>-0.5319102914976027</v>
+      </c>
+      <c r="M10">
+        <v>15</v>
+      </c>
+      <c r="N10">
+        <v>0.6025778249869023</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="Q10">
+        <v>0.300482349344105</v>
+      </c>
+      <c r="R10">
+        <v>-0.0366512499635458</v>
+      </c>
+      <c r="S10">
+        <v>0.6376159486517559</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11">
@@ -1253,6 +1527,32 @@
       <c r="K11">
         <v>1.670575427443796</v>
       </c>
+      <c r="L11">
+        <v>-0.5415527615639625</v>
+      </c>
+      <c r="M11">
+        <v>15</v>
+      </c>
+      <c r="N11">
+        <v>0.5960795120399227</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="Q11">
+        <v>0.3201722041285594</v>
+      </c>
+      <c r="R11">
+        <v>-0.01250303931275704</v>
+      </c>
+      <c r="S11">
+        <v>0.6528474475698758</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12">
@@ -1290,6 +1590,32 @@
       <c r="K12">
         <v>1.961806753907536</v>
       </c>
+      <c r="L12">
+        <v>-0.1718114363242738</v>
+      </c>
+      <c r="M12">
+        <v>12</v>
+      </c>
+      <c r="N12">
+        <v>0.8664491624514203</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="Q12">
+        <v>0.3683463276272237</v>
+      </c>
+      <c r="R12">
+        <v>-0.03248277948884987</v>
+      </c>
+      <c r="S12">
+        <v>0.7691754347432973</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13">
@@ -1327,6 +1653,32 @@
       <c r="K13">
         <v>1.670694787579001</v>
       </c>
+      <c r="L13">
+        <v>-0.5404691456012148</v>
+      </c>
+      <c r="M13">
+        <v>14</v>
+      </c>
+      <c r="N13">
+        <v>0.5973675451833442</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="Q13">
+        <v>0.3833427672804872</v>
+      </c>
+      <c r="R13">
+        <v>0.06359297770137806</v>
+      </c>
+      <c r="S13">
+        <v>0.7030925568595963</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14">
@@ -1364,6 +1716,32 @@
       <c r="K14">
         <v>1.698393469250904</v>
       </c>
+      <c r="L14">
+        <v>-0.5438907293276781</v>
+      </c>
+      <c r="M14">
+        <v>15</v>
+      </c>
+      <c r="N14">
+        <v>0.5945092115932444</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="Q14">
+        <v>0.2937355808048765</v>
+      </c>
+      <c r="R14">
+        <v>-0.0357081225216303</v>
+      </c>
+      <c r="S14">
+        <v>0.6231792841313832</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15">
@@ -1401,6 +1779,32 @@
       <c r="K15">
         <v>1.663937308768766</v>
       </c>
+      <c r="L15">
+        <v>-0.5454749838634741</v>
+      </c>
+      <c r="M15">
+        <v>15</v>
+      </c>
+      <c r="N15">
+        <v>0.593446330124793</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="Q15">
+        <v>0.3104715585290476</v>
+      </c>
+      <c r="R15">
+        <v>-0.01579687639489313</v>
+      </c>
+      <c r="S15">
+        <v>0.6367399934529884</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16">
@@ -1438,6 +1842,32 @@
       <c r="K16">
         <v>1.936835955360008</v>
       </c>
+      <c r="L16">
+        <v>-0.1783483178181479</v>
+      </c>
+      <c r="M16">
+        <v>12</v>
+      </c>
+      <c r="N16">
+        <v>0.8614249180377355</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="Q16">
+        <v>0.3608238944056711</v>
+      </c>
+      <c r="R16">
+        <v>-0.03059895780296362</v>
+      </c>
+      <c r="S16">
+        <v>0.7522467466143059</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17">
@@ -1475,6 +1905,32 @@
       <c r="K17">
         <v>1.653438718288825</v>
       </c>
+      <c r="L17">
+        <v>-0.5568775296539122</v>
+      </c>
+      <c r="M17">
+        <v>14</v>
+      </c>
+      <c r="N17">
+        <v>0.5864038628811856</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="Q17">
+        <v>0.374824680046364</v>
+      </c>
+      <c r="R17">
+        <v>0.06324098367547404</v>
+      </c>
+      <c r="S17">
+        <v>0.6864083764172541</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18">
@@ -1512,6 +1968,32 @@
       <c r="K18">
         <v>1.664530899193221</v>
       </c>
+      <c r="L18">
+        <v>-0.5585081277100347</v>
+      </c>
+      <c r="M18">
+        <v>15</v>
+      </c>
+      <c r="N18">
+        <v>0.5847389602588766</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="Q18">
+        <v>0.2850013866077366</v>
+      </c>
+      <c r="R18">
+        <v>-0.03340952748322562</v>
+      </c>
+      <c r="S18">
+        <v>0.6034123006986987</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19">
@@ -1549,6 +2031,32 @@
       <c r="K19">
         <v>1.639268809959219</v>
       </c>
+      <c r="L19">
+        <v>-0.5489298482449003</v>
+      </c>
+      <c r="M19">
+        <v>15</v>
+      </c>
+      <c r="N19">
+        <v>0.5911317833254313</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="Q19">
+        <v>0.2985397782505868</v>
+      </c>
+      <c r="R19">
+        <v>-0.01780500887650471</v>
+      </c>
+      <c r="S19">
+        <v>0.6148845653776782</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20">
@@ -1586,6 +2094,32 @@
       <c r="K20">
         <v>1.892272379614639</v>
       </c>
+      <c r="L20">
+        <v>-0.1855362356637336</v>
+      </c>
+      <c r="M20">
+        <v>12</v>
+      </c>
+      <c r="N20">
+        <v>0.855907596915511</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="Q20">
+        <v>0.3507976607974505</v>
+      </c>
+      <c r="R20">
+        <v>-0.02720842861396533</v>
+      </c>
+      <c r="S20">
+        <v>0.7288037502088663</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21">
@@ -1622,6 +2156,32 @@
       </c>
       <c r="K21">
         <v>1.618042952216723</v>
+      </c>
+      <c r="L21">
+        <v>-0.5789569992095736</v>
+      </c>
+      <c r="M21">
+        <v>14</v>
+      </c>
+      <c r="N21">
+        <v>0.5718161737434864</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="Q21">
+        <v>0.3637087559891199</v>
+      </c>
+      <c r="R21">
+        <v>0.06375747871288057</v>
+      </c>
+      <c r="S21">
+        <v>0.6636600332653593</v>
       </c>
     </row>
   </sheetData>
